--- a/artfynd/A 6423-2024 artfynd.xlsx
+++ b/artfynd/A 6423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2788,6 +2788,573 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>114953308</v>
+      </c>
+      <c r="B21" t="n">
+        <v>96510</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>572932</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6424002</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114953204</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>572933</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6423978</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114953180</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>572911</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6424024</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114953294</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>573006</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6424013</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114953257</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97545</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>573062</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6423974</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-03-01</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6423-2024 artfynd.xlsx
+++ b/artfynd/A 6423-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3355,6 +3355,3582 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>115003855</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>573369</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6424172</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>115003627</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>573347</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6424076</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>115004290</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>573217</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6423766</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>115003636</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>573326</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6424103</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>115003678</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>573331</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6424138</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>115004191</v>
+      </c>
+      <c r="B31" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>573189</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6423812</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>115003972</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>573360</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6424144</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>115004135</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>573364</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6424023</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>115004170</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>573189</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6423811</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>115003549</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>573104</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6423783</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>115003531</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>573099</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6423774</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>115003649</v>
+      </c>
+      <c r="B37" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>573327</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6424135</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>115004041</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>573359</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6424110</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>115004017</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>573359</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6424134</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115004063</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>573343</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6424140</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>115004074</v>
+      </c>
+      <c r="B41" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>573369</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6424090</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>115004148</v>
+      </c>
+      <c r="B42" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>573183</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6423813</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>115003753</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>573366</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6424153</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>115003952</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>573376</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6424140</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>115003602</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>573164</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6423899</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="inlineStr"/>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>115003902</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>573380</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6424153</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="inlineStr"/>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>115004255</v>
+      </c>
+      <c r="B47" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>573203</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6423785</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>115003824</v>
+      </c>
+      <c r="B48" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>573385</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6424163</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>115003662</v>
+      </c>
+      <c r="B49" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>573325</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6424128</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>115003701</v>
+      </c>
+      <c r="B50" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>573358</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6424194</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="inlineStr"/>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115003730</v>
+      </c>
+      <c r="B51" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>573367</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6424175</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115003994</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>573363</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6424143</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115004093</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>573368</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6424083</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>115003567</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>573091</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6423806</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>115004209</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>573191</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6423805</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115003927</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>573375</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6424151</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>115004230</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97555</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>A 6423, Skälhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>573186</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6423790</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Odensvi</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2024-03-04</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
